--- a/01-TamanhoFuncionalIA/Dashboard_English.xlsx
+++ b/01-TamanhoFuncionalIA/Dashboard_English.xlsx
@@ -11,7 +11,7 @@
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FFDD2B-939A-46FD-96AD-969E63C53881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="88hXoIgUtrnfspDW0pkfZNQ+NGITKcLKRpe8LqY15UjCxeP9/+++bMPH/vDaNDvs2YB/0BLL0MRKOOCDZ5+f4w==" workbookSaltValue="WKeoAyKgQENB7/mexnTR5w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{D9361617-B028-4F7E-8120-EB055563DB2B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="2" firstSheet="3" activeTab="3" xr2:uid="{D9361617-B028-4F7E-8120-EB055563DB2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Dif_PF_retorno" sheetId="2" state="hidden" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId6"/>
+    <pivotCache cacheId="54" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -899,7 +899,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -931,22 +931,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -994,268 +978,7 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="177">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
+  <dxfs count="90">
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
@@ -1766,40 +1489,40 @@
   </dxfs>
   <tableStyles count="5" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de Tabela 1" pivot="0" count="1" xr9:uid="{255CE0ED-0FD0-42A2-AAA4-6066EA1E3A73}">
-      <tableStyleElement type="wholeTable" dxfId="176"/>
+      <tableStyleElement type="wholeTable" dxfId="89"/>
     </tableStyle>
     <tableStyle name="Estilo de Tabela Dinâmica 1" table="0" count="1" xr9:uid="{7E2792C1-09BE-4B4F-BC27-86B4F0A0503B}">
-      <tableStyleElement type="wholeTable" dxfId="175"/>
+      <tableStyleElement type="wholeTable" dxfId="88"/>
     </tableStyle>
     <tableStyle name="PivotStyleLight16 2" table="0" count="11" xr9:uid="{130B00C2-B130-458B-ACD2-AB29A18ABD73}">
-      <tableStyleElement type="headerRow" dxfId="174"/>
-      <tableStyleElement type="totalRow" dxfId="173"/>
-      <tableStyleElement type="firstRowStripe" dxfId="172"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="171"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="170"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="169"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="168"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="167"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="166"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="165"/>
-      <tableStyleElement type="pageFieldValues" dxfId="164"/>
+      <tableStyleElement type="headerRow" dxfId="87"/>
+      <tableStyleElement type="totalRow" dxfId="86"/>
+      <tableStyleElement type="firstRowStripe" dxfId="85"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="84"/>
+      <tableStyleElement type="firstSubtotalColumn" dxfId="83"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="82"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="81"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="80"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="79"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="78"/>
+      <tableStyleElement type="pageFieldValues" dxfId="77"/>
     </tableStyle>
     <tableStyle name="PivotStyleLight16 3" table="0" count="11" xr9:uid="{B29E7EF6-F5E8-4D37-B206-7FC3602B5EAB}">
-      <tableStyleElement type="headerRow" dxfId="163"/>
-      <tableStyleElement type="totalRow" dxfId="162"/>
-      <tableStyleElement type="firstRowStripe" dxfId="161"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="160"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="159"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="158"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="157"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="156"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="155"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="154"/>
-      <tableStyleElement type="pageFieldValues" dxfId="153"/>
+      <tableStyleElement type="headerRow" dxfId="76"/>
+      <tableStyleElement type="totalRow" dxfId="75"/>
+      <tableStyleElement type="firstRowStripe" dxfId="74"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="73"/>
+      <tableStyleElement type="firstSubtotalColumn" dxfId="72"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="71"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="70"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="69"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="68"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="67"/>
+      <tableStyleElement type="pageFieldValues" dxfId="66"/>
     </tableStyle>
     <tableStyle name="SlicerStyleLight1 2" pivot="0" table="0" count="10" xr9:uid="{42DCEF36-D987-4582-A324-4AC330AF3A06}">
-      <tableStyleElement type="wholeTable" dxfId="152"/>
-      <tableStyleElement type="headerRow" dxfId="151"/>
+      <tableStyleElement type="wholeTable" dxfId="65"/>
+      <tableStyleElement type="headerRow" dxfId="64"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3474,7 +3197,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3746,6 +3469,30 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-1C17-40E8-A7CF-E27AA741C84A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="4"/>
@@ -3763,6 +3510,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-1C17-40E8-A7CF-E27AA741C84A}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -5575,7 +5325,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -9002,8 +8752,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>41275</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Demanda_Portugues">
@@ -9026,7 +8776,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9863,145 +9613,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D4D7B27-619C-408D-BBF4-814CA05132F6}" name="Tabela dinâmica19" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Média PF" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="119">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="118">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="117">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E21E3687-BE02-4E0C-A4EC-3D9C8F58E65D}" name="Tabela dinâmica18" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Média PF IA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="138">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="137">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="136">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFC09C96-8278-4C5A-B2BD-07649DA5D815}" name="Tabela dinâmica30" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFC09C96-8278-4C5A-B2BD-07649DA5D815}" name="Tabela dinâmica30" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="F1:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10088,7 +9700,7 @@
     <i/>
   </colItems>
   <formats count="1">
-    <format dxfId="139">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10104,8 +9716,146 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C06B2D20-8BF9-4037-BA28-CA09B03F157E}" name="Tabela dinâmica25" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C14:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" Diferença" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="49">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70C2C97E-64A8-4C17-9950-8E360C0346D7}" name="Tabela dinâmica22" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Máx. PF IA" fld="2" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="52">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10999F50-549D-4991-99C8-1285FC9BD5BD}" name="Tabela dinâmica23" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10999F50-549D-4991-99C8-1285FC9BD5BD}" name="Tabela dinâmica23" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
@@ -10151,13 +9901,13 @@
     <dataField name="Máx. PF" fld="1" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="142">
+    <format dxfId="55">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="141">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="140">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -10174,8 +9924,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C27D7DFE-20FE-41DD-A042-F0AED9114E18}" name="Tabela dinâmica24" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A14:A15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F2524E3-E908-434C-9438-38CB1C163D89}" name="Tabela dinâmica21" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C8:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -10189,11 +9939,11 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10217,16 +9967,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name=" %Erro" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Mín. PF IA" fld="2" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="145">
+    <format dxfId="58">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="144">
+    <format dxfId="57">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="143">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -10243,8 +9993,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5A6BFF9-D3FA-4454-9FF0-66BAF9C9BD54}" name="Tabela dinâmica17" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C2:C3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74461AFC-45FB-4085-8389-C7E62E2C2EFC}" name="Tabela dinâmica16" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -10257,8 +10007,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
@@ -10286,10 +10036,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma PF IA" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Soma PF" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="87">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -10306,677 +10056,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76D68026-9BC4-498F-A4AC-A1D990FAA9B5}" name="Tabela dinâmica22" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Máx. PF IA" fld="2" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="90">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="89">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="88">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74461AFC-45FB-4085-8389-C7E62E2C2EFC}" name="Tabela dinâmica16" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma PF" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="91">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{89B18B92-11FF-46A3-9F5D-FBAF1A1F16DA}" name="Tabela dinâmica21" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C8:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Mín. PF IA" fld="2" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="94">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="93">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="92">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF40D9DB-8C6F-4570-AD83-D7B3C5CAF358}" name="Tabela dinâmica27" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="L1:N8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Soma de PF" fld="1" baseField="0" baseItem="0"/>
-    <dataField name="Soma de PF_IA" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="95">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49A5E453-897A-4708-949C-1CC4D3550F21}" name="Tabela dinâmica20" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A8:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Mín. PF" fld="1" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="98">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="97">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="96">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C06B2D20-8BF9-4037-BA28-CA09B03F157E}" name="Tabela dinâmica25" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C14:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" Diferença" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="122">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="121">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="120">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C6E4A46-131D-49FD-BB3A-3508722CE395}" name="Tabela dinâmica25" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C14:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" Diferença" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="101">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="100">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="99">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1F71617-A4AE-43FC-94D2-33E893D5A9DA}" name="Tabela dinâmica19" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Média PF" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="104">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="103">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="102">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45074D50-6FCF-47D8-AFCD-6259FCE5B193}" name="Tabela dinâmica24" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A14:A15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" %Erro" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="107">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="106">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="105">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C34A0A17-E659-4636-B3F8-203037848848}" name="Tabela dinâmica30" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C34A0A17-E659-4636-B3F8-203037848848}" name="Tabela dinâmica30" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="F1:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -11054,7 +10134,7 @@
     <i/>
   </colItems>
   <formats count="1">
-    <format dxfId="108">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11070,8 +10150,568 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3453BEE-2C3F-4B63-A677-C4812E79AC35}" name="Tabela dinâmica29" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{632187B4-2119-4573-996B-DBFBE670F574}" name="Tabela dinâmica23" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Máx. PF" fld="1" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="4">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF40D9DB-8C6F-4570-AD83-D7B3C5CAF358}" name="Tabela dinâmica27" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="L1:N8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Soma de PF" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Soma de PF_IA" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="5">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A1F71617-A4AE-43FC-94D2-33E893D5A9DA}" name="Tabela dinâmica19" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média PF" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="8">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76D68026-9BC4-498F-A4AC-A1D990FAA9B5}" name="Tabela dinâmica22" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Máx. PF IA" fld="2" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="11">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7103E362-2821-4398-AA37-EC74A1941F59}" name="Tabela dinâmica27" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="L1:N8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name=" PF" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="PF AI" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C26F47B-4293-40D7-BC46-515D5B783559}" name="Tabela dinâmica18" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média PF IA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="14">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D3453BEE-2C3F-4B63-A677-C4812E79AC35}" name="Tabela dinâmica29" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -11149,7 +10789,7 @@
     <i/>
   </colItems>
   <formats count="1">
-    <format dxfId="109">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11165,146 +10805,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C26F47B-4293-40D7-BC46-515D5B783559}" name="Tabela dinâmica18" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Média PF IA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="112">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="111">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="110">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{632187B4-2119-4573-996B-DBFBE670F574}" name="Tabela dinâmica23" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Máx. PF" fld="1" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="115">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="114">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="113">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F59BD2B-203D-4453-BD0D-2EC4765167A2}" name="Tabela dinâmica28" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F59BD2B-203D-4453-BD0D-2EC4765167A2}" name="Tabela dinâmica28" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="L11:N18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0">
@@ -11382,7 +10884,7 @@
     <dataField name=" Diferença" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="116">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11430,9 +10932,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC046600-9FF0-4C76-9033-7777A4D0CA22}" name="Tabela dinâmica20" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A8:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C6E4A46-131D-49FD-BB3A-3508722CE395}" name="Tabela dinâmica25" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C14:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -11445,13 +10947,13 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11474,16 +10976,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Mín. PF" fld="1" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name=" Diferença" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="125">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="124">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="123">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -11499,11 +11001,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7103E362-2821-4398-AA37-EC74A1941F59}" name="Tabela dinâmica27" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="L1:N8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49A5E453-897A-4708-949C-1CC4D3550F21}" name="Tabela dinâmica20" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A8:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
         <item x="1"/>
@@ -11513,20 +11015,149 @@
         <item x="5"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Mín. PF" fld="1" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45074D50-6FCF-47D8-AFCD-6259FCE5B193}" name="Tabela dinâmica24" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A14:A15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" %Erro" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5A6BFF9-D3FA-4454-9FF0-66BAF9C9BD54}" name="Tabela dinâmica17" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C2:C3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11545,108 +11176,215 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <rowItems count="1">
+    <i/>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="2">
-    <dataField name=" PF" fld="1" baseField="0" baseItem="0"/>
-    <dataField name="PF AI" fld="2" baseField="0" baseItem="0"/>
+  <dataFields count="1">
+    <dataField name="Soma PF IA" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="126">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="6">
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{89B18B92-11FF-46A3-9F5D-FBAF1A1F16DA}" name="Tabela dinâmica21" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C8:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Mín. PF IA" fld="2" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="29">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE858B6D-278A-4C67-B410-B28D61BB27E2}" name="Tabela dinâmica17" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C2:C3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma PF IA" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="32">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7557456E-DCF7-4A9A-B126-E878701D79BD}" name="Tabela dinâmica16" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma PF" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="33">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -11660,8 +11398,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F2524E3-E908-434C-9438-38CB1C163D89}" name="Tabela dinâmica21" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C8:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E21E3687-BE02-4E0C-A4EC-3D9C8F58E65D}" name="Tabela dinâmica18" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -11703,16 +11441,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Mín. PF IA" fld="2" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Média PF IA" fld="2" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="129">
+    <format dxfId="36">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -11729,8 +11467,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7557456E-DCF7-4A9A-B126-E878701D79BD}" name="Tabela dinâmica16" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:A3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC046600-9FF0-4C76-9033-7777A4D0CA22}" name="Tabela dinâmica20" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A8:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -11772,11 +11510,17 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma PF" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Mín. PF" fld="1" subtotal="min" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="130">
+  <formats count="3">
+    <format dxfId="39">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -11792,8 +11536,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE858B6D-278A-4C67-B410-B28D61BB27E2}" name="Tabela dinâmica17" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C2:C3" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C27D7DFE-20FE-41DD-A042-F0AED9114E18}" name="Tabela dinâmica24" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A14:A15" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="22">
     <pivotField showAll="0">
       <items count="7">
@@ -11807,11 +11551,11 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11835,11 +11579,17 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Soma PF IA" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name=" %Erro" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="131">
+  <formats count="3">
+    <format dxfId="42">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -11855,7 +11605,76 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91E1A854-D071-400F-9431-3A9D6FCB18A0}" name="Tabela dinâmica28" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D4D7B27-619C-408D-BBF4-814CA05132F6}" name="Tabela dinâmica19" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="22">
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média PF" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="45">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91E1A854-D071-400F-9431-3A9D6FCB18A0}" name="Tabela dinâmica28" cacheId="54" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
   <location ref="L11:N18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" showAll="0">
@@ -11933,7 +11752,7 @@
     <dataField name=" Diference" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="132">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12041,75 +11860,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70C2C97E-64A8-4C17-9950-8E360C0346D7}" name="Tabela dinâmica22" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="22">
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Máx. PF IA" fld="2" subtotal="max" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="135">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="134">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="133">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DadosExternos_1" connectionId="1" xr16:uid="{99999CDD-27CD-4D20-A88F-7AD22989207D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="23" unboundColumnsRight="1">
@@ -12183,15 +11933,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D95F7AA2-02D7-434F-BEC9-3FBB450FD5B4}" name="Dif_PF_retorno" displayName="Dif_PF_retorno" ref="A1:V7" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:V7" xr:uid="{D95F7AA2-02D7-434F-BEC9-3FBB450FD5B4}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{AF770FB7-7C33-47ED-BE92-BC2ECB51BC61}" uniqueName="1" name="Demanda" queryTableFieldId="1" dataDxfId="150"/>
+    <tableColumn id="1" xr3:uid="{AF770FB7-7C33-47ED-BE92-BC2ECB51BC61}" uniqueName="1" name="Demanda" queryTableFieldId="1" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{3660F3F2-B6C4-4528-B0D2-12E1C7BA5376}" uniqueName="2" name="PF" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{43E10021-2405-4546-BF49-8C284955F946}" uniqueName="3" name="PF_IA" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{BB2D3556-970A-4E65-A134-485454839B99}" uniqueName="4" name="EscopoResumido" queryTableFieldId="4" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{35D9108D-B970-45E4-AE82-95B6C77D44A5}" uniqueName="5" name="ResumoErros" queryTableFieldId="5" dataDxfId="148"/>
-    <tableColumn id="6" xr3:uid="{9B4B3B43-E604-4C64-9590-D0FA9DA6A360}" uniqueName="6" name="Data contagem" queryTableFieldId="6" dataDxfId="147"/>
+    <tableColumn id="4" xr3:uid="{BB2D3556-970A-4E65-A134-485454839B99}" uniqueName="4" name="EscopoResumido" queryTableFieldId="4" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{35D9108D-B970-45E4-AE82-95B6C77D44A5}" uniqueName="5" name="ResumoErros" queryTableFieldId="5" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{9B4B3B43-E604-4C64-9590-D0FA9DA6A360}" uniqueName="6" name="Data contagem" queryTableFieldId="6" dataDxfId="60"/>
     <tableColumn id="7" xr3:uid="{0FEBAF32-32FB-4F95-9EC7-1A5AD0B7FED3}" uniqueName="7" name="%Erro" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{C5F68BD5-901C-4D2B-8E0E-22B6CAF0B2AE}" uniqueName="8" name="Diferenca" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{F037F8D1-55F8-4CD3-96D0-18D2FF1834AD}" uniqueName="9" name="Justificativa" queryTableFieldId="9" dataDxfId="146"/>
+    <tableColumn id="9" xr3:uid="{F037F8D1-55F8-4CD3-96D0-18D2FF1834AD}" uniqueName="9" name="Justificativa" queryTableFieldId="9" dataDxfId="59"/>
     <tableColumn id="10" xr3:uid="{6DB34CDA-AC6B-4656-BE1D-2C602603B0BD}" uniqueName="10" name="Minimo_PF" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{F53C52F6-51FD-4092-9832-D1E9C9F36699}" uniqueName="11" name="Minimo_PF_IA" queryTableFieldId="11"/>
     <tableColumn id="12" xr3:uid="{63CA7D9F-AF1B-4408-A8EF-031DB150B652}" uniqueName="12" name="Maximo_PF" queryTableFieldId="12"/>
@@ -13969,108 +13719,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="20">
+      <c r="A3" s="5"/>
+      <c r="B3" s="13">
         <f>'Tabelas-English'!A4</f>
         <v>38.58</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="13">
         <f>'Tabelas-English'!A7</f>
         <v>6.43</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="13">
         <f>'Tabelas-English'!A10</f>
         <v>3.68</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="13">
         <f>'Tabelas-English'!A13</f>
         <v>9.6</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="13">
         <f>'Tabelas-English'!A16</f>
         <v>281.41606280193236</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="13">
         <f>'Tabelas-English'!C16</f>
         <v>100.41999999999999</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="13">
         <f>'Tabelas-English'!C4</f>
         <v>139</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="13">
         <f>'Tabelas-English'!C7</f>
         <v>23.166666666666668</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="13">
         <f>'Tabelas-English'!C10</f>
         <v>4</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="13">
         <f>'Tabelas-English'!C13</f>
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
